--- a/events/Poznan_2012_WC/Poznan_2012_WC_Results.xlsx
+++ b/events/Poznan_2012_WC/Poznan_2012_WC_Results.xlsx
@@ -49403,11 +49403,6 @@
           <t>1:58.321</t>
         </is>
       </c>
-      <c r="S758" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -63886,11 +63881,6 @@
           <t>1:53.821</t>
         </is>
       </c>
-      <c r="S985" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
@@ -83056,11 +83046,6 @@
       <c r="P1281" t="inlineStr">
         <is>
           <t>1:54.544</t>
-        </is>
-      </c>
-      <c r="S1281" t="inlineStr">
-        <is>
-          <t>133041</t>
         </is>
       </c>
     </row>
@@ -92519,7 +92504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D280"/>
+  <dimension ref="A1:D279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98575,34 +98560,34 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>133041</t>
+          <t>60015</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>Peng</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>ZHANG</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>60015</t>
+          <t>52182</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Peng</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -98612,19 +98597,19 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>52182</t>
+          <t>61025</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Yu</t>
+          <t>Yubo</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -98634,49 +98619,27 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>61025</t>
+          <t>42179</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Yubo</t>
+          <t>Milenko</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>ZHOU</t>
+          <t>ZORIC</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>42179</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Milenko</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>ZORIC</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Poznan_2012_WC/Poznan_2012_WC_Results.xlsx
+++ b/events/Poznan_2012_WC/Poznan_2012_WC_Results.xlsx
@@ -3536,6 +3536,11 @@
           <t>2:06.892</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3976,6 +3981,11 @@
           <t>3:51.790</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4666,6 +4676,11 @@
           <t>4:01.063</t>
         </is>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4856,6 +4871,11 @@
           <t>4:34.135</t>
         </is>
       </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>54666</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5350,6 +5370,11 @@
           <t>3:55.548</t>
         </is>
       </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5410,6 +5435,11 @@
           <t>3:58.692</t>
         </is>
       </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5600,6 +5630,11 @@
           <t>3:50.942</t>
         </is>
       </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6550,6 +6585,11 @@
           <t>3:57.002</t>
         </is>
       </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>36498</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -11478,6 +11518,11 @@
           <t>3:34.993</t>
         </is>
       </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
       <c r="S175" t="inlineStr">
         <is>
           <t>42452</t>
@@ -11878,6 +11923,11 @@
           <t>36048</t>
         </is>
       </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>36049</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -12393,6 +12443,11 @@
           <t>3:39.155</t>
         </is>
       </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
       <c r="S189" t="inlineStr">
         <is>
           <t>45846</t>
@@ -12643,6 +12698,11 @@
           <t>4:24.775</t>
         </is>
       </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>54666</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12983,6 +13043,11 @@
           <t>46372</t>
         </is>
       </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>89760</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -14548,6 +14613,11 @@
           <t>1:37.822</t>
         </is>
       </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>35176</t>
+        </is>
+      </c>
       <c r="U222" t="inlineStr">
         <is>
           <t>35700</t>
@@ -14613,6 +14683,11 @@
           <t>1:40.350</t>
         </is>
       </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -15113,6 +15188,11 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -16323,6 +16403,11 @@
           <t>2:12.324</t>
         </is>
       </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -17622,6 +17707,11 @@
           <t>3:48.132</t>
         </is>
       </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -18587,6 +18677,11 @@
           <t>4:05.052</t>
         </is>
       </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -18957,6 +19052,11 @@
           <t>3:59.036</t>
         </is>
       </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -22861,6 +22961,11 @@
           <t>3:31.490</t>
         </is>
       </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
       <c r="S353" t="inlineStr">
         <is>
           <t>45846</t>
@@ -23051,6 +23156,11 @@
           <t>3:36.562</t>
         </is>
       </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
       <c r="S356" t="inlineStr">
         <is>
           <t>42452</t>
@@ -23251,6 +23361,11 @@
           <t>36048</t>
         </is>
       </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>36049</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -24551,6 +24666,11 @@
           <t>46372</t>
         </is>
       </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>89760</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -26256,6 +26376,11 @@
           <t>1:52.612</t>
         </is>
       </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -27581,6 +27706,11 @@
           <t>1:55.062</t>
         </is>
       </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -27821,6 +27951,11 @@
           <t>2:10.774</t>
         </is>
       </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>54666</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -28631,6 +28766,11 @@
           <t>2:08.424</t>
         </is>
       </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>63214</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -30335,6 +30475,11 @@
           <t>2:08.647</t>
         </is>
       </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>54666</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -31330,6 +31475,11 @@
           <t>1:43.030</t>
         </is>
       </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
       <c r="S485" t="inlineStr">
         <is>
           <t>52286</t>
@@ -32980,6 +33130,11 @@
           <t>42046</t>
         </is>
       </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
       <c r="T509" t="inlineStr">
         <is>
           <t>41991</t>
@@ -33055,6 +33210,11 @@
           <t>42727</t>
         </is>
       </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>42735</t>
+        </is>
+      </c>
       <c r="T510" t="inlineStr">
         <is>
           <t>42731</t>
@@ -33140,6 +33300,11 @@
           <t>36153</t>
         </is>
       </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -34600,6 +34765,11 @@
           <t>1:51.133</t>
         </is>
       </c>
+      <c r="R534" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -35480,6 +35650,11 @@
           <t>2:01.803</t>
         </is>
       </c>
+      <c r="R548" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -36345,6 +36520,11 @@
           <t>2:10.447</t>
         </is>
       </c>
+      <c r="R562" t="inlineStr">
+        <is>
+          <t>63214</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -36665,6 +36845,11 @@
           <t>1:38.507</t>
         </is>
       </c>
+      <c r="R567" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
       <c r="S567" t="inlineStr">
         <is>
           <t>52286</t>
@@ -38330,6 +38515,11 @@
           <t>42727</t>
         </is>
       </c>
+      <c r="S592" t="inlineStr">
+        <is>
+          <t>42735</t>
+        </is>
+      </c>
       <c r="T592" t="inlineStr">
         <is>
           <t>42731</t>
@@ -38490,6 +38680,11 @@
           <t>36153</t>
         </is>
       </c>
+      <c r="U594" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -39974,6 +40169,11 @@
           <t>3:56.123</t>
         </is>
       </c>
+      <c r="R617" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -42365,6 +42565,11 @@
           <t>3:36.106</t>
         </is>
       </c>
+      <c r="R654" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
       <c r="S654" t="inlineStr">
         <is>
           <t>45846</t>
@@ -42710,6 +42915,11 @@
           <t>46372</t>
         </is>
       </c>
+      <c r="S659" t="inlineStr">
+        <is>
+          <t>89760</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -42782,6 +42992,11 @@
           <t>52177</t>
         </is>
       </c>
+      <c r="T660" t="inlineStr">
+        <is>
+          <t>63214</t>
+        </is>
+      </c>
       <c r="U660" t="inlineStr">
         <is>
           <t>47675</t>
@@ -44953,6 +45168,11 @@
           <t>3:43.449</t>
         </is>
       </c>
+      <c r="R693" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -46020,6 +46240,11 @@
           <t>36048</t>
         </is>
       </c>
+      <c r="S709" t="inlineStr">
+        <is>
+          <t>36049</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -46983,6 +47208,11 @@
           <t>46372</t>
         </is>
       </c>
+      <c r="S723" t="inlineStr">
+        <is>
+          <t>89760</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -47184,6 +47414,11 @@
           <t>1:39.573</t>
         </is>
       </c>
+      <c r="T726" t="inlineStr">
+        <is>
+          <t>35176</t>
+        </is>
+      </c>
       <c r="U726" t="inlineStr">
         <is>
           <t>35700</t>
@@ -47410,6 +47645,11 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T729" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -47693,6 +47933,11 @@
           <t>1:44.057</t>
         </is>
       </c>
+      <c r="T733" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -48274,6 +48519,11 @@
           <t>42046</t>
         </is>
       </c>
+      <c r="S741" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
       <c r="T741" t="inlineStr">
         <is>
           <t>41991</t>
@@ -48351,6 +48601,11 @@
           <t>42727</t>
         </is>
       </c>
+      <c r="S742" t="inlineStr">
+        <is>
+          <t>42735</t>
+        </is>
+      </c>
       <c r="T742" t="inlineStr">
         <is>
           <t>42731</t>
@@ -49083,6 +49338,11 @@
           <t>1:51.633</t>
         </is>
       </c>
+      <c r="S753" t="inlineStr">
+        <is>
+          <t>35176</t>
+        </is>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -51633,6 +51893,11 @@
           <t>0:39.336</t>
         </is>
       </c>
+      <c r="R793" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -52378,6 +52643,11 @@
           <t>0:48.999</t>
         </is>
       </c>
+      <c r="R805" t="inlineStr">
+        <is>
+          <t>54666</t>
+        </is>
+      </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
@@ -53543,6 +53813,11 @@
           <t>0:43.192</t>
         </is>
       </c>
+      <c r="R824" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
@@ -57317,6 +57592,11 @@
           <t>0:44.576</t>
         </is>
       </c>
+      <c r="R884" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
@@ -57692,6 +57972,11 @@
           <t>0:43.412</t>
         </is>
       </c>
+      <c r="R890" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
@@ -60012,6 +60297,11 @@
           <t>0:36.775</t>
         </is>
       </c>
+      <c r="R926" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
       <c r="S926" t="inlineStr">
         <is>
           <t>52232</t>
@@ -60537,6 +60827,11 @@
           <t>0:34.639</t>
         </is>
       </c>
+      <c r="R934" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
       <c r="S934" t="inlineStr">
         <is>
           <t>52286</t>
@@ -61262,6 +61557,11 @@
           <t>0:36.098</t>
         </is>
       </c>
+      <c r="R945" t="inlineStr">
+        <is>
+          <t>36498</t>
+        </is>
+      </c>
       <c r="S945" t="inlineStr">
         <is>
           <t>36499</t>
@@ -61327,6 +61627,11 @@
           <t>0:45.534</t>
         </is>
       </c>
+      <c r="R946" t="inlineStr">
+        <is>
+          <t>54666</t>
+        </is>
+      </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
@@ -62506,6 +62811,11 @@
           <t>0:39.876</t>
         </is>
       </c>
+      <c r="R964" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
@@ -64441,6 +64751,11 @@
           <t>0:38.497</t>
         </is>
       </c>
+      <c r="R994" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
@@ -66376,6 +66691,11 @@
           <t>0:41.953</t>
         </is>
       </c>
+      <c r="R1025" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
@@ -68775,6 +69095,11 @@
           <t>0:44.445</t>
         </is>
       </c>
+      <c r="R1063" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
@@ -69345,6 +69670,11 @@
           <t>0:43.164</t>
         </is>
       </c>
+      <c r="R1072" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
@@ -72455,6 +72785,11 @@
           <t>0:34.444</t>
         </is>
       </c>
+      <c r="R1120" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
       <c r="S1120" t="inlineStr">
         <is>
           <t>52286</t>
@@ -73758,6 +74093,11 @@
           <t>0:39.314</t>
         </is>
       </c>
+      <c r="R1140" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
@@ -76620,6 +76960,11 @@
           <t>0:44.868</t>
         </is>
       </c>
+      <c r="R1184" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
@@ -77424,6 +77769,11 @@
           <t>0:38.847</t>
         </is>
       </c>
+      <c r="R1196" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
       <c r="S1196" t="inlineStr">
         <is>
           <t>52286</t>
@@ -78719,6 +79069,11 @@
           <t>0:42.365</t>
         </is>
       </c>
+      <c r="R1216" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
@@ -79426,6 +79781,11 @@
           <t>0:43.725</t>
         </is>
       </c>
+      <c r="R1227" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
@@ -81069,6 +81429,11 @@
           <t>0:40.617</t>
         </is>
       </c>
+      <c r="R1251" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
@@ -82316,6 +82681,11 @@
           <t>1:49.632</t>
         </is>
       </c>
+      <c r="S1270" t="inlineStr">
+        <is>
+          <t>35176</t>
+        </is>
+      </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
@@ -84162,6 +84532,11 @@
           <t>1:55.276</t>
         </is>
       </c>
+      <c r="R1298" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
@@ -84730,6 +85105,11 @@
           <t>2:12.441</t>
         </is>
       </c>
+      <c r="R1307" t="inlineStr">
+        <is>
+          <t>63214</t>
+        </is>
+      </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
@@ -86785,6 +87165,11 @@
           <t>1:37.795</t>
         </is>
       </c>
+      <c r="R1338" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
       <c r="S1338" t="inlineStr">
         <is>
           <t>52286</t>
@@ -89959,6 +90344,11 @@
           <t>19:52.145</t>
         </is>
       </c>
+      <c r="R1387" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
@@ -90872,6 +91262,11 @@
           <t>21:28.677</t>
         </is>
       </c>
+      <c r="R1401" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
@@ -92019,6 +92414,11 @@
       <c r="L1419" t="n">
         <v>38</v>
       </c>
+      <c r="R1419" t="inlineStr">
+        <is>
+          <t>127223</t>
+        </is>
+      </c>
       <c r="X1419" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -92131,6 +92531,11 @@
       <c r="L1421" t="n">
         <v>21</v>
       </c>
+      <c r="R1421" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
       <c r="X1421" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -92425,6 +92830,11 @@
       </c>
       <c r="L1426" t="n">
         <v>3</v>
+      </c>
+      <c r="R1426" t="inlineStr">
+        <is>
+          <t>54666</t>
+        </is>
       </c>
       <c r="X1426" t="inlineStr">
         <is>
@@ -92504,7 +92914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D279"/>
+  <dimension ref="A1:D301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98645,6 +99055,490 @@
         </is>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>35176</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Karolin</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>WAGNER</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>36049</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>COSGAYA</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>ANOSHKIN</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>SHTYL</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>PODOLSKAIA</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>WALKER</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Joana</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>SOUSA</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>36498</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Jose Giovanny</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>RAMOS</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Miika</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>NYKAENEN</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Aleh</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>YURENIA</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Volha</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>KHUDZENKA</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Aliksandr</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>LIAPIOSHKA</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Kenny</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>WALLACE</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Timothy</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>HORNSBY</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>MEHAK</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>42735</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Nelson Roberto</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>GERINGER SALLETE</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Vitalii</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>TSURKAN</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Aleksey</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>MOCHALOV</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>54666</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Nasreddine</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>BAGHDADI</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>63214</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Nurislom</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>TUKHTASIN UGLI</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>89760</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Oleksandr</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>SIVKOV</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>127223</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Aliaksandr</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>YERMAKOU</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Poznan_2012_WC/Poznan_2012_WC_Results.xlsx
+++ b/events/Poznan_2012_WC/Poznan_2012_WC_Results.xlsx
@@ -2026,11 +2026,6 @@
           <t>2:02.644</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>99700</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3031,11 +3026,6 @@
           <t>2:06.652</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>47779</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7600,11 +7590,6 @@
           <t>4:33.099</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>66277</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9730,11 +9715,6 @@
           <t>4:35.919</t>
         </is>
       </c>
-      <c r="R147" t="inlineStr">
-        <is>
-          <t>99700</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10534,11 +10514,6 @@
       <c r="L160" t="n">
         <v>5</v>
       </c>
-      <c r="R160" t="inlineStr">
-        <is>
-          <t>47779</t>
-        </is>
-      </c>
       <c r="X160" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -15833,11 +15808,6 @@
           <t>2:10.003</t>
         </is>
       </c>
-      <c r="R240" t="inlineStr">
-        <is>
-          <t>99700</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -16908,11 +16878,6 @@
           <t>2:12.772</t>
         </is>
       </c>
-      <c r="R257" t="inlineStr">
-        <is>
-          <t>47779</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -21452,11 +21417,6 @@
           <t>4:58.868</t>
         </is>
       </c>
-      <c r="R329" t="inlineStr">
-        <is>
-          <t>66277</t>
-        </is>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -21761,11 +21721,6 @@
           <t>4:34.950</t>
         </is>
       </c>
-      <c r="R334" t="inlineStr">
-        <is>
-          <t>99700</t>
-        </is>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -31880,11 +31835,6 @@
           <t>47673</t>
         </is>
       </c>
-      <c r="S491" t="inlineStr">
-        <is>
-          <t>52177</t>
-        </is>
-      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -33370,11 +33320,6 @@
           <t>46399</t>
         </is>
       </c>
-      <c r="S512" t="inlineStr">
-        <is>
-          <t>55865</t>
-        </is>
-      </c>
       <c r="T512" t="inlineStr">
         <is>
           <t>46414</t>
@@ -38595,11 +38540,6 @@
           <t>46399</t>
         </is>
       </c>
-      <c r="S593" t="inlineStr">
-        <is>
-          <t>55865</t>
-        </is>
-      </c>
       <c r="T593" t="inlineStr">
         <is>
           <t>46414</t>
@@ -39132,11 +39072,6 @@
           <t>2:10.250</t>
         </is>
       </c>
-      <c r="R601" t="inlineStr">
-        <is>
-          <t>99700</t>
-        </is>
-      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -42987,11 +42922,6 @@
           <t>52229</t>
         </is>
       </c>
-      <c r="S660" t="inlineStr">
-        <is>
-          <t>52177</t>
-        </is>
-      </c>
       <c r="T660" t="inlineStr">
         <is>
           <t>63214</t>
@@ -43456,11 +43386,6 @@
           <t>4:33.367</t>
         </is>
       </c>
-      <c r="R667" t="inlineStr">
-        <is>
-          <t>99700</t>
-        </is>
-      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -48683,11 +48608,6 @@
           <t>46399</t>
         </is>
       </c>
-      <c r="S743" t="inlineStr">
-        <is>
-          <t>55865</t>
-        </is>
-      </c>
       <c r="T743" t="inlineStr">
         <is>
           <t>46414</t>
@@ -49663,6 +49583,11 @@
           <t>1:58.321</t>
         </is>
       </c>
+      <c r="S758" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -54773,11 +54698,6 @@
           <t>0:45.358</t>
         </is>
       </c>
-      <c r="R839" t="inlineStr">
-        <is>
-          <t>52177</t>
-        </is>
-      </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
@@ -59567,11 +59487,6 @@
           <t>46414</t>
         </is>
       </c>
-      <c r="S915" t="inlineStr">
-        <is>
-          <t>55865</t>
-        </is>
-      </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
@@ -60762,11 +60677,6 @@
           <t>0:33.867</t>
         </is>
       </c>
-      <c r="S933" t="inlineStr">
-        <is>
-          <t>42139</t>
-        </is>
-      </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
@@ -64191,6 +64101,11 @@
           <t>1:53.821</t>
         </is>
       </c>
+      <c r="S985" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
@@ -68775,11 +68690,6 @@
           <t>0:45.369</t>
         </is>
       </c>
-      <c r="R1058" t="inlineStr">
-        <is>
-          <t>52177</t>
-        </is>
-      </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
@@ -71455,11 +71365,6 @@
           <t>0:33.777</t>
         </is>
       </c>
-      <c r="S1100" t="inlineStr">
-        <is>
-          <t>42139</t>
-        </is>
-      </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
@@ -71650,11 +71555,6 @@
           <t>46414</t>
         </is>
       </c>
-      <c r="S1103" t="inlineStr">
-        <is>
-          <t>55865</t>
-        </is>
-      </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
@@ -77496,11 +77396,6 @@
           <t>0:34.643</t>
         </is>
       </c>
-      <c r="S1192" t="inlineStr">
-        <is>
-          <t>42139</t>
-        </is>
-      </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
@@ -83418,6 +83313,11 @@
           <t>1:54.544</t>
         </is>
       </c>
+      <c r="S1281" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
@@ -87726,11 +87626,6 @@
           <t>47673</t>
         </is>
       </c>
-      <c r="S1346" t="inlineStr">
-        <is>
-          <t>52177</t>
-        </is>
-      </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
@@ -88539,11 +88434,6 @@
           <t>24:53.785</t>
         </is>
       </c>
-      <c r="R1358" t="inlineStr">
-        <is>
-          <t>66277</t>
-        </is>
-      </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
@@ -89079,11 +88969,6 @@
       <c r="P1367" t="inlineStr">
         <is>
           <t>23:08.577</t>
-        </is>
-      </c>
-      <c r="R1367" t="inlineStr">
-        <is>
-          <t>47779</t>
         </is>
       </c>
     </row>
@@ -92914,7 +92799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D301"/>
+  <dimension ref="A1:D296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93008,17 +92893,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>66277</t>
+          <t>42199</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Adnan</t>
+          <t>Kaarel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ALIEV</t>
+          <t>ALUPERE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -93030,17 +92915,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>42199</t>
+          <t>35866</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kaarel</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ALUPERE</t>
+          <t>AMBROZIAK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -93052,61 +92937,61 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>35866</t>
+          <t>47908</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Sabrina Ines</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AMBROZIAK</t>
+          <t>AMEGHINO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>47908</t>
+          <t>52747</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sabrina Ines</t>
+          <t>Farzin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AMEGHINO</t>
+          <t>ASADI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>52747</t>
+          <t>68983</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Farzin</t>
+          <t>Romans</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ASADI</t>
+          <t>ASTAPOVS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -93118,17 +93003,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>68983</t>
+          <t>42035</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Romans</t>
+          <t>Aliaksandr</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ASTAPOVS</t>
+          <t>BAHDANOVICH</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -93140,12 +93025,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>42035</t>
+          <t>42040</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aliaksandr</t>
+          <t>Andrei</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -93162,17 +93047,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42040</t>
+          <t>35285</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Andrei</t>
+          <t>Adrien</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BAHDANOVICH</t>
+          <t>BART</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -93184,61 +93069,61 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>35285</t>
+          <t>42442</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Adrien</t>
+          <t>Genevieve</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BART</t>
+          <t>BEAUCHESNE-SEVIGNY</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>42442</t>
+          <t>35288</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Genevieve</t>
+          <t>Maxime</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BEAUCHESNE-SEVIGNY</t>
+          <t>BEAUMONT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>35288</t>
+          <t>52158</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Maxime</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BEAUMONT</t>
+          <t>BECERRA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -93250,83 +93135,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>52158</t>
+          <t>42549</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Afef</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BECERRA</t>
+          <t>BEN ISMAIL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>36063</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Krisztina</t>
+          <t>Alfonso</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BEDOCS</t>
+          <t>BENAVIDES</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>42549</t>
+          <t>44433</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Afef</t>
+          <t>Lubomir</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BEN ISMAIL</t>
+          <t>BENO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>36063</t>
+          <t>42727</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alfonso</t>
+          <t>Juan Pablo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BENAVIDES</t>
+          <t>BERGERO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -93338,17 +93223,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>44433</t>
+          <t>35291</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lubomir</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BENO</t>
+          <t>BEUGNET</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -93360,17 +93245,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>42727</t>
+          <t>36384</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Juan Pablo</t>
+          <t>Sergiy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BERGERO</t>
+          <t>BEZUGLIY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -93382,17 +93267,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>35291</t>
+          <t>42049</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Vitaliy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BEUGNET</t>
+          <t>BIALKO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -93404,17 +93289,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>36384</t>
+          <t>46764</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sergiy</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BEZUGLIY</t>
+          <t>BIRD</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -93426,105 +93311,105 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>42049</t>
+          <t>69144</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vitaliy</t>
+          <t>Lissa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BIALKO</t>
+          <t>BISSONNETTE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>46764</t>
+          <t>126240</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Jana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BIRD</t>
+          <t>BLAHOVA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>69144</t>
+          <t>53327</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lissa</t>
+          <t>Kasemsit</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BISSONNETTE</t>
+          <t>BORRIBOONWASIN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>126240</t>
+          <t>52232</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jana</t>
+          <t>Sergey</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BLAHOVA</t>
+          <t>BORZOV</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>53327</t>
+          <t>35698</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kasemsit</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BORRIBOONWASIN</t>
+          <t>BRENDEL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -93536,105 +93421,105 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>52232</t>
+          <t>48772</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sergey</t>
+          <t>Lize</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BORZOV</t>
+          <t>BROEKX</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>35698</t>
+          <t>35984</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Agnes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BRENDEL</t>
+          <t>BRUN-LIE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>48772</t>
+          <t>42447</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lize</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BROEKX</t>
+          <t>BRYANT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>35984</t>
+          <t>35299</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Agnes</t>
+          <t>Cyrille</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BRUN-LIE</t>
+          <t>CARRE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>42447</t>
+          <t>42729</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Gonzalo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BRYANT</t>
+          <t>CARRERAS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -93646,39 +93531,39 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>35299</t>
+          <t>36282</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cyrille</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CARRE</t>
+          <t>CARRINGTON</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>42729</t>
+          <t>36405</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gonzalo</t>
+          <t>Miguel Angel</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CARRERAS</t>
+          <t>CASTANEDA CASTILLO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -93690,39 +93575,39 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>36282</t>
+          <t>36404</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Saul</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CARRINGTON</t>
+          <t>CASTILLO MORALES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36405</t>
+          <t>41785</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Miguel Angel</t>
+          <t>Olivier</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CASTANEDA CASTILLO</t>
+          <t>CAUWENBERGH</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -93734,39 +93619,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>36404</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Saul</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CASTILLO MORALES</t>
+          <t>CAWTHORN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>41785</t>
+          <t>46354</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Olivier</t>
+          <t>Iurii</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CAUWENBERGH</t>
+          <t>CHEBAN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -93778,17 +93663,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>35813</t>
+          <t>36343</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Jiemei Sarah</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CAWTHORN</t>
+          <t>CHEN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -93800,17 +93685,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>46354</t>
+          <t>36153</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Iurii</t>
+          <t>Nikolay</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CHEBAN</t>
+          <t>CHERVOV</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -93822,39 +93707,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>36343</t>
+          <t>45846</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jiemei Sarah</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CHEN</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>36153</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nikolay</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CHERVOV</t>
+          <t>COCHRANE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -93866,17 +93751,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>45846</t>
+          <t>42725</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Miguel</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>CORREA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -93888,17 +93773,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>42449</t>
+          <t>36045</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Saul</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>COCHRANE</t>
+          <t>CRAVIOTTO</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -93910,17 +93795,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>42725</t>
+          <t>36399</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Miguel</t>
+          <t>Everardo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CORREA</t>
+          <t>CRISTOBAL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -93932,17 +93817,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>36045</t>
+          <t>36043</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Saul</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CRAVIOTTO</t>
+          <t>CUBELOS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -93954,17 +93839,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>36399</t>
+          <t>42724</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Everardo</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CRISTOBAL</t>
+          <t>DAL BO</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -93976,17 +93861,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>36043</t>
+          <t>35782</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CUBELOS</t>
+          <t>DAVIDEK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -93998,17 +93883,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>42724</t>
+          <t>42733</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DAL BO</t>
+          <t>DE ANDRES</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -94020,17 +93905,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>35782</t>
+          <t>42262</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Cesar</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DAVIDEK</t>
+          <t>DE CESARE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -94042,17 +93927,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>42733</t>
+          <t>42732</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Juan Pablo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DE ANDRES</t>
+          <t>DE GESUS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -94064,17 +93949,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>42262</t>
+          <t>42731</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cesar</t>
+          <t>Pablo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DE CESARE</t>
+          <t>DE TORRES</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -94086,17 +93971,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>42732</t>
+          <t>44424</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Juan Pablo</t>
+          <t>Viktor</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DE GESUS</t>
+          <t>DEMIN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -94108,17 +93993,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>42731</t>
+          <t>42571</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pablo</t>
+          <t>Alexey</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DE TORRES</t>
+          <t>DERGUNOV</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -94130,17 +94015,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>44424</t>
+          <t>36604</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Viktor</t>
+          <t>Miika</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DEMIN</t>
+          <t>DIETRICH</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -94152,39 +94037,39 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>42571</t>
+          <t>35700</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Alexey</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DERGUNOV</t>
+          <t>DIETZE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>36604</t>
+          <t>42377</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Miika</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DIETRICH</t>
+          <t>DOMEISEN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -94196,39 +94081,39 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>35700</t>
+          <t>35777</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Josef</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DIETZE</t>
+          <t>DOSTAL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>42377</t>
+          <t>42452</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Philippe</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DOMEISEN</t>
+          <t>DUCHESNEAU</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -94240,17 +94125,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>36143</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Josef</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DOSTAL</t>
+          <t>DYACHENKO</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -94262,105 +94147,105 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>42452</t>
+          <t>36002</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Philippe</t>
+          <t>Edyta</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DUCHESNEAU</t>
+          <t>DZIENISZEWSKA KIERKLA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>36143</t>
+          <t>42797</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DYACHENKO</t>
+          <t>EGAN-SIMMONS</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>42798</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Edyta</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DZIENISZEWSKA KIERKLA</t>
+          <t>EGAN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>42797</t>
+          <t>36205</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Dmitrii</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>EGAN-SIMMONS</t>
+          <t>EKIMOV</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>42798</t>
+          <t>46599</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Engin</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EGAN</t>
+          <t>ERKAN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -94372,39 +94257,39 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>36205</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dmitrii</t>
+          <t>Eliana</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>EKIMOV</t>
+          <t>ESCALONA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>46599</t>
+          <t>36450</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Engin</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ERKAN</t>
+          <t>FERNANDES</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -94416,39 +94301,39 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>36503</t>
+          <t>36280</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Eliana</t>
+          <t>Darryl</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ESCALONA</t>
+          <t>FITZGERALD</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>36450</t>
+          <t>35927</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Pawel</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FERNANDES</t>
+          <t>FLORCZAK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -94460,39 +94345,39 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>36280</t>
+          <t>42453</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Darryl</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FITZGERALD</t>
+          <t>FOURNEL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>35927</t>
+          <t>42455</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pawel</t>
+          <t>Hughes</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FLORCZAK</t>
+          <t>FOURNEL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -94504,39 +94389,39 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>35554</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FOURNEL</t>
+          <t>FUKSA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>42455</t>
+          <t>46418</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hughes</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FOURNEL</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -94548,17 +94433,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>35554</t>
+          <t>44434</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FUKSA</t>
+          <t>GELLE</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -94570,39 +94455,39 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>46418</t>
+          <t>36457</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Beatriz</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GOMES</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>44434</t>
+          <t>56336</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Vyacheslav</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GELLE</t>
+          <t>GORN</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -94614,39 +94499,39 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>36457</t>
+          <t>35318</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Beatriz</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GOMES</t>
+          <t>GOUBEL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>56336</t>
+          <t>35705</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Vyacheslav</t>
+          <t>Marcus</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GORN</t>
+          <t>GROSS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -94658,17 +94543,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>35318</t>
+          <t>46596</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Mustafa</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GOUBEL</t>
+          <t>GULBAHAR</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -94680,17 +94565,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>99700</t>
+          <t>35321</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GRISHINA</t>
+          <t>GUYOT</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -94702,61 +94587,61 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>35705</t>
+          <t>35924</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Eef</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GROSS</t>
+          <t>HAAZE</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>46596</t>
+          <t>52762</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Mustafa</t>
+          <t>Arezou</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GULBAHAR</t>
+          <t>HAKIMIMOGHADDAM</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>35321</t>
+          <t>42337</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Henriette Engel</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GUYOT</t>
+          <t>HANSEN</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -94768,39 +94653,39 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>35924</t>
+          <t>42042</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Eef</t>
+          <t>Dzianis</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HAAZE</t>
+          <t>HARAZHA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>52762</t>
+          <t>36391</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Arezou</t>
+          <t>Bridgitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HAKIMIMOGHADDAM</t>
+          <t>HARTLEY</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -94812,17 +94697,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>36283</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Henriette Engel</t>
+          <t>Teneale</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HANSEN</t>
+          <t>HATTON</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -94834,17 +94719,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>42042</t>
+          <t>35555</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dzianis</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HARAZHA</t>
+          <t>HAVEL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -94856,61 +94741,61 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>36391</t>
+          <t>36228</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bridgitte</t>
+          <t>Liam</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HARTLEY</t>
+          <t>HEATH</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>64874</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Teneale</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HATTON</t>
+          <t>HENRIQUES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>35555</t>
+          <t>36048</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HAVEL</t>
+          <t>HERNANZ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -94922,17 +94807,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>36228</t>
+          <t>35707</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Liam</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HEATH</t>
+          <t>HOFF</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -94944,17 +94829,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>64874</t>
+          <t>35708</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nelson</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HENRIQUES</t>
+          <t>HOLLSTEIN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -94966,17 +94851,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>42175</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Ervin</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HERNANZ</t>
+          <t>HOLPERT</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -94988,17 +94873,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>35707</t>
+          <t>35709</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HOFF</t>
+          <t>HOLTZ</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -95010,17 +94895,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>35708</t>
+          <t>42548</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HOLLSTEIN</t>
+          <t>HOUCINE</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -95032,17 +94917,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>42175</t>
+          <t>35324</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ervin</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HOLPERT</t>
+          <t>HYBOIS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -95054,17 +94939,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>35709</t>
+          <t>46372</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Dmytro</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HOLTZ</t>
+          <t>IANCHUK</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -95076,17 +94961,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>42548</t>
+          <t>69073</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Vilyam</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HOUCINE</t>
+          <t>IBRAGIMOV</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -95098,17 +94983,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>35324</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Gabor</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HYBOIS</t>
+          <t>JAKUBIK</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -95120,17 +95005,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>35912</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Dmytro</t>
+          <t>Tomas</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>IANCHUK</t>
+          <t>JANDA</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -95142,17 +95027,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>69073</t>
+          <t>44435</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Vilyam</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>IBRAGIMOV</t>
+          <t>JANKOVEC</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -95164,17 +95049,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>44425</t>
+          <t>42441</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Gabor</t>
+          <t>Andrzej</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>JAKUBIK</t>
+          <t>JEZIERSKI</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -95186,61 +95071,61 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>35912</t>
+          <t>36502</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Angelica</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>JANDA</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>44435</t>
+          <t>49753</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Michaela</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>JANKOVEC</t>
+          <t>LINDBLAD JONSSON</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>42441</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Andrzej</t>
+          <t>Sebastien</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>JEZIERSKI</t>
+          <t>JOUVE</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -95252,17 +95137,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>36502</t>
+          <t>47909</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Angelica</t>
+          <t>Alexandra Borbala</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>KERESZTESI</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -95274,39 +95159,39 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>49753</t>
+          <t>35713</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Michaela</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LINDBLAD JONSSON</t>
+          <t>KIRAJ</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>35328</t>
+          <t>46122</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sebastien</t>
+          <t>Miroslav</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>JOUVE</t>
+          <t>KIRCHEV</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -95318,17 +95203,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>47909</t>
+          <t>118949</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Alexandra Borbala</t>
+          <t>Inna</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>KERESZTESI</t>
+          <t>KLINOVA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -95340,39 +95225,39 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>35713</t>
+          <t>44421</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Ivana</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>KIRAJ</t>
+          <t>KMETOVA</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>46122</t>
+          <t>65136</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Miroslav</t>
+          <t>Antons</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>KIRCHEV</t>
+          <t>KNESIS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -95384,39 +95269,39 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>118949</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Inna</t>
+          <t>Gerasim</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>KLINOVA</t>
+          <t>KOCHNEV</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>44421</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ivana</t>
+          <t>Dorota</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>KMETOVA</t>
+          <t>KOZAKIEWICZ</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -95428,17 +95313,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>65136</t>
+          <t>147929</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Antons</t>
+          <t>Jiri</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>KNESIS</t>
+          <t>KRAFT</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -95450,17 +95335,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>47675</t>
+          <t>45732</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Gerasim</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>KOCHNEV</t>
+          <t>KRAJCOVIC</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -95472,39 +95357,39 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>36001</t>
+          <t>35937</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Dorota</t>
+          <t>Arkadiusz</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>KOZAKIEWICZ</t>
+          <t>KRAJEWSKI</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>147929</t>
+          <t>35715</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Jiri</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>KRAFT</t>
+          <t>KRETSCHMER</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -95516,17 +95401,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>45732</t>
+          <t>35872</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Michal</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>KRAJCOVIC</t>
+          <t>KUDLA</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -95538,17 +95423,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Arkadiusz</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>KRAJEWSKI</t>
+          <t>KULETA</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -95560,17 +95445,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>35715</t>
+          <t>46597</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Ozturk</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>KRETSCHMER</t>
+          <t>KURU</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -95582,17 +95467,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>35872</t>
+          <t>35717</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Michal</t>
+          <t>Kurt</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>KUDLA</t>
+          <t>KUSCHELA</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -95604,61 +95489,61 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>35986</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Mira Veraas</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>KULETA</t>
+          <t>LARSEN</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>46597</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ozturk</t>
+          <t>Ana-Roxana</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>KURU</t>
+          <t>LEHACI</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>35717</t>
+          <t>64070</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Kurt</t>
+          <t>Tony Gill</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>KUSCHELA</t>
+          <t>LESPOIR</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -95670,17 +95555,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>35986</t>
+          <t>52169</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Mira Veraas</t>
+          <t>Zhangli</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LARSEN</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -95692,127 +95577,127 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>99871</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ana-Roxana</t>
+          <t>Marko</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LEHACI</t>
+          <t>LIPOVAC</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>64070</t>
+          <t>52167</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Tony Gill</t>
+          <t>Haiping</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>LESPOIR</t>
+          <t>LIU</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>52169</t>
+          <t>42771</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Zhangli</t>
+          <t>Nikica</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LJUBEK</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>99871</t>
+          <t>36165</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Marko</t>
+          <t>Natalia</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>LIPOVAC</t>
+          <t>LOBOVA</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>52167</t>
+          <t>36389</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Haiping</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LIU</t>
+          <t>LOUW</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>42771</t>
+          <t>36154</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nikica</t>
+          <t>Kirill</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LJUBEK</t>
+          <t>LUCHKIN</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -95824,39 +95709,39 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>36165</t>
+          <t>42887</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Stefo</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LOBOVA</t>
+          <t>LUTZ</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>36389</t>
+          <t>42044</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Vadzim</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>LOUW</t>
+          <t>MAKHNEU</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -95868,17 +95753,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>36154</t>
+          <t>46385</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Kirill</t>
+          <t>Oleksandr</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>LUCHKIN</t>
+          <t>MAKSYMCHUK</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -95890,17 +95775,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>42887</t>
+          <t>35928</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Stefo</t>
+          <t>Rafal</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>LUTZ</t>
+          <t>MARON</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -95912,39 +95797,39 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>42044</t>
+          <t>35897</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Vadzim</t>
+          <t>Lucie</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MAKHNEU</t>
+          <t>MATOUSKOVA</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>46385</t>
+          <t>45290</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Oleksandr</t>
+          <t>Momotaro</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MAKSYMCHUK</t>
+          <t>MATSUSHITA</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -95956,39 +95841,39 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>42139</t>
+          <t>35391</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ruslan</t>
+          <t>Joanne</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MAMUTOV</t>
+          <t>MAYER</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>35928</t>
+          <t>35867</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Rafal</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MARON</t>
+          <t>MAZUR</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -96000,83 +95885,83 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>35897</t>
+          <t>42487</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Lucie</t>
+          <t>Jason Stephen Reginald</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MATOUSKOVA</t>
+          <t>MCCOOMBS</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>45290</t>
+          <t>42361</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Momotaro</t>
+          <t>Kaitlyn</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MATSUSHITA</t>
+          <t>MCELROY</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>35391</t>
+          <t>36226</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Joanne</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MAYER</t>
+          <t>MCKEEVER</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>35867</t>
+          <t>47673</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Vadim</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MAZUR</t>
+          <t>MENKOV</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -96088,17 +95973,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>42487</t>
+          <t>42046</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Jason Stephen Reginald</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MCCOOMBS</t>
+          <t>MIADZVEDZEU</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -96110,17 +95995,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>42361</t>
+          <t>46102</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Kaitlyn</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MCELROY</t>
+          <t>MILLAN</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -96132,17 +96017,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>36226</t>
+          <t>52229</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Serik</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MCKEEVER</t>
+          <t>MIRBEKOV</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -96154,39 +96039,39 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>52177</t>
+          <t>42187</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Merey</t>
+          <t>Nikolina</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MEDETOV</t>
+          <t>MOLDOVAN</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>47673</t>
+          <t>36141</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Vadim</t>
+          <t>Maxim</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MENKOV</t>
+          <t>MOLOCHKOV</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -96198,61 +96083,61 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>42046</t>
+          <t>36412</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Maricela</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MIADZVEDZEU</t>
+          <t>MONTEMAYOR RODRIGUEZ</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>46102</t>
+          <t>42283</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Mohamed Ali</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MILLAN</t>
+          <t>MRABET</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>52229</t>
+          <t>48048</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Serik</t>
+          <t>Zaza</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>MIRBEKOV</t>
+          <t>NADIRADZE</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -96264,17 +96149,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>42187</t>
+          <t>35557</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Nikolina</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MOLDOVAN</t>
+          <t>NAJA</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -96286,17 +96171,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>36141</t>
+          <t>36798</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Maxim</t>
+          <t>Ignas</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MOLOCHKOV</t>
+          <t>NAVAKAUSKAS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -96308,61 +96193,61 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>36412</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Maricela</t>
+          <t>Ricardas</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MONTEMAYOR RODRIGUEZ</t>
+          <t>NEKRIOSIUS</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>42283</t>
+          <t>45837</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Mohamed Ali</t>
+          <t>Alana</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>MRABET</t>
+          <t>NICHOLLS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>48048</t>
+          <t>61432</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Zaza</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>NADIRADZE</t>
+          <t>NICOLAS</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -96374,39 +96259,39 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>35557</t>
+          <t>36140</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>NAJA</t>
+          <t>NIKOLAEV</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>36798</t>
+          <t>42181</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ignas</t>
+          <t>Marko</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>NAVAKAUSKAS</t>
+          <t>NOVAKOVIC</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -96418,17 +96303,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>35723</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Ricardas</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>NEKRIOSIUS</t>
+          <t>NUCK</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -96440,17 +96325,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>45837</t>
+          <t>45329</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Alana</t>
+          <t>Asumi</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>NICHOLLS</t>
+          <t>OHMURA</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -96462,17 +96347,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>61432</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Mark William</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>NICOLAS</t>
+          <t>OLDERSHAW</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -96484,17 +96369,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>36140</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Andrej</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>NIKOLAEV</t>
+          <t>OLIJNIK</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -96506,17 +96391,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>42181</t>
+          <t>36635</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Marko</t>
+          <t>Ronilson Matias De</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>NOVAKOVIC</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -96528,61 +96413,61 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>35723</t>
+          <t>46100</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Ysumy</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>NUCK</t>
+          <t>ORELLANA</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>45329</t>
+          <t>36499</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Asumi</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>OHMURA</t>
+          <t>OROPEZA</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>64876</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Mark William</t>
+          <t>Fortunato</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>OLDERSHAW</t>
+          <t>PACAVIRA</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -96594,17 +96479,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Andrej</t>
+          <t>Dejan</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>OLIJNIK</t>
+          <t>PAJIC</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -96616,83 +96501,83 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>36635</t>
+          <t>51871</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ronilson Matias De</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>PALDANIUS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>46100</t>
+          <t>41784</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Ysumy</t>
+          <t>Laurens</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ORELLANA</t>
+          <t>PANNECOUCKE</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>36499</t>
+          <t>42059</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Nadzeya</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>OROPEZA</t>
+          <t>PAPOK</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>64876</t>
+          <t>36495</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Fortunato</t>
+          <t>Edwar</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PACAVIRA</t>
+          <t>PAREDES PADRON</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -96704,17 +96589,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>42178</t>
+          <t>36046</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Dejan</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PAJIC</t>
+          <t>PEREZ RIAL</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -96726,17 +96611,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>51871</t>
+          <t>41793</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Hermien</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PALDANIUS</t>
+          <t>PETERS</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -96748,17 +96633,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>41784</t>
+          <t>42569</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Laurens</t>
+          <t>Vladimir</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>PANNECOUCKE</t>
+          <t>PETROV</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -96770,39 +96655,39 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>42059</t>
+          <t>45847</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Nadzeya</t>
+          <t>Jesse</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PAPOK</t>
+          <t>PHILLIPS</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>36495</t>
+          <t>41991</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Edwar</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PAREDES PADRON</t>
+          <t>PIATRUSHENKA</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -96814,17 +96699,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>36046</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PEREZ RIAL</t>
+          <t>PIMENTA</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -96836,17 +96721,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>41793</t>
+          <t>36033</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Hermien</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>PETERS</t>
+          <t>PIPITSOULI</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -96858,17 +96743,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>42569</t>
+          <t>53954</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Vladimir</t>
+          <t>Bartosz</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>PETROV</t>
+          <t>PLAWSKI</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -96880,17 +96765,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>45847</t>
+          <t>36150</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Jesse</t>
+          <t>Vasily</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>PHILLIPS</t>
+          <t>POGREBAN</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -96902,61 +96787,61 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>41991</t>
+          <t>36598</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>Pauliina</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>PIATRUSHENKA</t>
+          <t>POLET</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>36448</t>
+          <t>36313</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Spela</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>PIMENTA</t>
+          <t>PONOMARENKO JANIC</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>36033</t>
+          <t>36455</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Teresa</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>PIPITSOULI</t>
+          <t>PORTELA</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -96968,17 +96853,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>53954</t>
+          <t>36005</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>PLAWSKI</t>
+          <t>POSPIECH</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -96990,17 +96875,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>36150</t>
+          <t>42336</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Vasily</t>
+          <t>Rene Holten</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>POGREBAN</t>
+          <t>POULSEN</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -97012,83 +96897,83 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>36598</t>
+          <t>47524</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Pauliina</t>
+          <t>Gatis</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>POLET</t>
+          <t>PRANKS</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>36313</t>
+          <t>42052</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Spela</t>
+          <t>Dzmitry</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>PONOMARENKO JANIC</t>
+          <t>RABCHANKA</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>36455</t>
+          <t>36496</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Teresa</t>
+          <t>Ronny</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>PORTELA</t>
+          <t>RATIA</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>36005</t>
+          <t>35724</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>POSPIECH</t>
+          <t>RAUHE</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -97100,17 +96985,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>42336</t>
+          <t>42468</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Rene Holten</t>
+          <t>Brady Daniel Heim</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>POULSEN</t>
+          <t>REARDON</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -97122,17 +97007,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>47524</t>
+          <t>36230</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Gatis</t>
+          <t>Kristian</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>PRANKS</t>
+          <t>REEVES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -97144,39 +97029,39 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>42052</t>
+          <t>52168</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Dzmitry</t>
+          <t>Wenjun</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>RABCHANKA</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>36496</t>
+          <t>42726</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Ronny</t>
+          <t>Ruben</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>RATIA</t>
+          <t>VOISARD REZOLA</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -97188,17 +97073,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>35724</t>
+          <t>41786</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Maxime</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>RAUHE</t>
+          <t>RICHARD</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -97210,83 +97095,83 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>42468</t>
+          <t>61165</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Brady Daniel Heim</t>
+          <t>Mariecarmen</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>REARDON</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>36456</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Kristian</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>REEVES</t>
+          <t>RODRIGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>52168</t>
+          <t>42481</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Wenjun</t>
+          <t>Aaron Joshua</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>RUBLEE</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>42726</t>
+          <t>36593</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Ruben</t>
+          <t>Aleksejs</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>VOISARD REZOLA</t>
+          <t>RUMJANCEVS</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -97298,17 +97183,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>41786</t>
+          <t>44427</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Maxime</t>
+          <t>Matej</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>RICHARD</t>
+          <t>RUSNAK</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -97320,39 +97205,39 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>61165</t>
+          <t>42471</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Mariecarmen</t>
+          <t>Benjamin Rolph Mathew</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RUSSELL</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>42483</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Helena</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>RODRIGUES</t>
+          <t>RUSSELL</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -97364,61 +97249,61 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>42481</t>
+          <t>52739</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Aaron Joshua</t>
+          <t>Nicole</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>RUBLEE</t>
+          <t>RUTISHAUSER</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>36593</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Aleksejs</t>
+          <t>Anele</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>RUMJANCEVS</t>
+          <t>SAKALYTE</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>44427</t>
+          <t>45294</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Matej</t>
+          <t>Naoya</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>RUSNAK</t>
+          <t>SAKAMOTO</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -97430,61 +97315,61 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>42471</t>
+          <t>36170</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Benjamin Rolph Mathew</t>
+          <t>Iuliana</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>RUSSELL</t>
+          <t>SALAKHOVA</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>42483</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>RUSSELL</t>
+          <t>SALBU</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>52739</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Nicole</t>
+          <t>Zulmarys</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>RUTISHAUSER</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -97496,61 +97381,61 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>36815</t>
+          <t>36229</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Anele</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>SAKALYTE</t>
+          <t>SCHOFIELD</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>45294</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Naoya</t>
+          <t>Yvonne</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>SAKAMOTO</t>
+          <t>SCHURING</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>36170</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Iuliana</t>
+          <t>Viktoria</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>SALAKHOVA</t>
+          <t>SCHWARZ</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -97562,39 +97447,39 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>42573</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Natalya</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>SALBU</t>
+          <t>SERGEYEVA</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>36500</t>
+          <t>56337</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Zulmarys</t>
+          <t>Ekaterina</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SHUBINA</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -97606,17 +97491,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>36229</t>
+          <t>35567</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Mario</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>SCHOFIELD</t>
+          <t>SIEGL</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -97628,105 +97513,105 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Yvonne</t>
+          <t>Emanuel</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>SCHURING</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>35560</t>
+          <t>35409</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Viktoria</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>SCHWARZ</t>
+          <t>SIMART</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>42573</t>
+          <t>105917</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Natalya</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>SERGEYEVA</t>
+          <t>SITKOWSKI</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>56337</t>
+          <t>46399</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Ekaterina</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>SHUBINA</t>
+          <t>SKORYK</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>35567</t>
+          <t>35980</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Mario</t>
+          <t>Jo Sondre</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>SIEGL</t>
+          <t>SOLHAUG</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -97738,17 +97623,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>36449</t>
+          <t>36634</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Emanuel</t>
+          <t>Erlon</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>DE SOUZA SILVA</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -97760,17 +97645,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>35409</t>
+          <t>42341</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Emil Staer</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>SIMART</t>
+          <t>SIMENSEN</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -97782,39 +97667,39 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>105917</t>
+          <t>46062</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Staniliya</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>SITKOWSKI</t>
+          <t>STAMENOVA</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>46399</t>
+          <t>35776</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>SKORYK</t>
+          <t>STERBA</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -97826,17 +97711,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>35980</t>
+          <t>35728</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Jo Sondre</t>
+          <t>Kostja</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>SOLHAUG</t>
+          <t>STROINSKI</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -97848,17 +97733,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>36634</t>
+          <t>35550</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Erlon</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>DE SOUZA SILVA</t>
+          <t>SVAB</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -97870,17 +97755,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>42341</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Emil Staer</t>
+          <t>Pawel</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>SIMENSEN</t>
+          <t>SZANDRACH</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -97892,39 +97777,39 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>46062</t>
+          <t>35931</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Staniliya</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>STAMENOVA</t>
+          <t>SZYPULA</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>35776</t>
+          <t>46101</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Johnnathan</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>STERBA</t>
+          <t>TAFRA</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -97936,17 +97821,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>47543</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Kostja</t>
+          <t>Ahmadreza</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>STROINSKI</t>
+          <t>TALEBIAN</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -97958,17 +97843,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>35550</t>
+          <t>61140</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Tauirai</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>SVAB</t>
+          <t>TEITI</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -97980,17 +97865,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>35934</t>
+          <t>52225</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Pawel</t>
+          <t>Artur</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>SZANDRACH</t>
+          <t>TOM</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -98002,17 +97887,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>35931</t>
+          <t>42184</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Marko</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>SZYPULA</t>
+          <t>TOMICEVIC</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -98024,17 +97909,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>46101</t>
+          <t>66559</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Johnnathan</t>
+          <t>Tarmo</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>TAFRA</t>
+          <t>TOOTSI</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -98046,17 +97931,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>47543</t>
+          <t>46419</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Ahmadreza</t>
+          <t>Alvaro</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>TALEBIAN</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -98068,17 +97953,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>61140</t>
+          <t>43664</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Tauirai</t>
+          <t>Serguey</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>TEITI</t>
+          <t>TORRES MADRIGAL</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -98090,17 +97975,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>55865</t>
+          <t>35553</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Sergii</t>
+          <t>Lukas</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>TOKARNYTSKYI</t>
+          <t>TREFIL</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -98112,17 +97997,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>52225</t>
+          <t>46414</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Artur</t>
+          <t>Ihor</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>TOM</t>
+          <t>TRUNOV</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -98134,39 +98019,39 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>42184</t>
+          <t>35415</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Marko</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>TOMICEVIC</t>
+          <t>TULEU</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>66559</t>
+          <t>42054</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Tarmo</t>
+          <t>Dzmitry</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>TOOTSI</t>
+          <t>VAITSISHKIN</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -98178,17 +98063,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>46419</t>
+          <t>52286</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Alvaro</t>
+          <t>Taras</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VALKO</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -98200,17 +98085,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>43664</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Serguey</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>TORRES MADRIGAL</t>
+          <t>VAN KOEVERDEN</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -98222,17 +98107,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>35553</t>
+          <t>42493</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Lukas</t>
+          <t>Roland</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>TREFIL</t>
+          <t>VARGA</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -98244,39 +98129,39 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>46414</t>
+          <t>36458</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Ihor</t>
+          <t>Joana</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>TRUNOV</t>
+          <t>VASCONCELOS</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>35415</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Oona</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>TULEU</t>
+          <t>VASKO</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -98288,17 +98173,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>42054</t>
+          <t>42053</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Dzmitry</t>
+          <t>Aliaksandr</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>VAITSISHKIN</t>
+          <t>VAUCHETSKI</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -98310,17 +98195,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>52286</t>
+          <t>99727</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Taras</t>
+          <t>Martins</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>VALKO</t>
+          <t>VEISPALS</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -98332,17 +98217,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>35729</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>VAN KOEVERDEN</t>
+          <t>VERCH</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -98354,17 +98239,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>42493</t>
+          <t>36595</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Roland</t>
+          <t>Niklas</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>VARGA</t>
+          <t>VETTANEN</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -98376,39 +98261,39 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>36458</t>
+          <t>36314</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Joana</t>
+          <t>Tilen</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>VASCONCELOS</t>
+          <t>VIDOVIC</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>36600</t>
+          <t>42883</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Oona</t>
+          <t>Laurence</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>VASKO</t>
+          <t>VINCENT-LAPOINTE</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -98420,17 +98305,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>42053</t>
+          <t>45725</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Aliaksandr</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>VAUCHETSKI</t>
+          <t>VLCEK</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -98442,61 +98327,61 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>99727</t>
+          <t>35730</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Martins</t>
+          <t>Sabine</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>VEISPALS</t>
+          <t>VOLZ</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>35729</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>VERCH</t>
+          <t>WALCZYKIEWICZ</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>36595</t>
+          <t>35930</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Niklas</t>
+          <t>Oskar</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>VETTANEN</t>
+          <t>WARSZAWSKI</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -98508,17 +98393,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>36314</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Tilen</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>VIDOVIC</t>
+          <t>WATKINS</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -98530,17 +98415,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>42883</t>
+          <t>35558</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Laurence</t>
+          <t>Ewelina</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>VINCENT-LAPOINTE</t>
+          <t>WOJNAROWSKA</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -98552,83 +98437,83 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>45725</t>
+          <t>52171</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Yanan</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>VLCEK</t>
+          <t>WU</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>35730</t>
+          <t>35737</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Sabine</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>VOLZ</t>
+          <t>WYLENZEK</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>WALCZYKIEWICZ</t>
+          <t>WYSS</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>35930</t>
+          <t>61026</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Oskar</t>
+          <t>Haitao</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>WARSZAWSKI</t>
+          <t>XU</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -98640,17 +98525,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Alexandr</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>WATKINS</t>
+          <t>YEMELYANOV</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -98662,61 +98547,61 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>35558</t>
+          <t>42562</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Ewelina</t>
+          <t>Mikhail</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>WOJNAROWSKA</t>
+          <t>YEMELYANOV</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>52171</t>
+          <t>42561</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Yanan</t>
+          <t>Sergey</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>WU</t>
+          <t>YEMELYANOV</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>35737</t>
+          <t>42563</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Timofey</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>WYLENZEK</t>
+          <t>YEMELYANOV</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -98728,17 +98613,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>46593</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Cagribey</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>WYSS</t>
+          <t>YILDIRIM</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -98750,17 +98635,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>61026</t>
+          <t>36149</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Haitao</t>
+          <t>Vitaly</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>XU</t>
+          <t>YURCHENKO</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -98772,17 +98657,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>42567</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Alexandr</t>
+          <t>Jost</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>YEMELYANOV</t>
+          <t>ZAKRAJSEK</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -98794,39 +98679,39 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>42562</t>
+          <t>64705</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Mikhail</t>
+          <t>Fabiola</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>YEMELYANOV</t>
+          <t>ZAMORANO</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>42561</t>
+          <t>44432</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Sergey</t>
+          <t>Miroslav</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>YEMELYANOV</t>
+          <t>ZATKO</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -98838,17 +98723,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>42563</t>
+          <t>60015</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Timofey</t>
+          <t>Peng</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>YEMELYANOV</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -98860,39 +98745,39 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>46593</t>
+          <t>52182</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Cagribey</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>YILDIRIM</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>36149</t>
+          <t>61025</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Vitaly</t>
+          <t>Yubo</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>YURCHENKO</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -98904,17 +98789,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>36310</t>
+          <t>42179</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Jost</t>
+          <t>Milenko</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>ZAKRAJSEK</t>
+          <t>ZORIC</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -98926,17 +98811,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>64705</t>
+          <t>35176</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Fabiola</t>
+          <t>Karolin</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>ZAMORANO</t>
+          <t>WAGNER</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -98948,17 +98833,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>44432</t>
+          <t>36049</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Miroslav</t>
+          <t>Diego</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>ZATKO</t>
+          <t>COSGAYA</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -98970,17 +98855,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>60015</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Peng</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>ZHOU</t>
+          <t>ANOSHKIN</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -98992,83 +98877,83 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>52182</t>
+          <t>36155</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Yu</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>ZHOU</t>
+          <t>SHTYL</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>61025</t>
+          <t>36164</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Yubo</t>
+          <t>Natalia</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>ZHOU</t>
+          <t>PODOLSKAIA</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>42179</t>
+          <t>36222</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Milenko</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>ZORIC</t>
+          <t>WALKER</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>35176</t>
+          <t>36459</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Karolin</t>
+          <t>Joana</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>WAGNER</t>
+          <t>SOUSA</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -99080,17 +98965,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>36049</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Diego</t>
+          <t>Jose Giovanny</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>COSGAYA</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -99102,17 +98987,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>36146</t>
+          <t>36596</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>Miika</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>ANOSHKIN</t>
+          <t>NYKAENEN</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -99124,17 +99009,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>36155</t>
+          <t>42045</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Aleh</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>SHTYL</t>
+          <t>YURENIA</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -99146,17 +99031,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>36164</t>
+          <t>42058</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Volha</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>PODOLSKAIA</t>
+          <t>KHUDZENKA</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -99168,61 +99053,61 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>36222</t>
+          <t>42063</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Aliksandr</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>WALKER</t>
+          <t>LIAPIOSHKA</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>36459</t>
+          <t>42161</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Joana</t>
+          <t>Kenny</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>SOUSA</t>
+          <t>WALLACE</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>36498</t>
+          <t>42358</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Jose Giovanny</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>HORNSBY</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -99234,17 +99119,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>36596</t>
+          <t>42463</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Miika</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>NYKAENEN</t>
+          <t>MEHAK</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -99256,17 +99141,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>42045</t>
+          <t>42735</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Aleh</t>
+          <t>Nelson Roberto</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>YURENIA</t>
+          <t>GERINGER SALLETE</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -99278,39 +99163,39 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>42058</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Volha</t>
+          <t>Vitalii</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>KHUDZENKA</t>
+          <t>TSURKAN</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>42063</t>
+          <t>52228</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Aliksandr</t>
+          <t>Aleksey</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>LIAPIOSHKA</t>
+          <t>MOCHALOV</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -99322,17 +99207,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>54666</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Kenny</t>
+          <t>Nasreddine</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>WALLACE</t>
+          <t>BAGHDADI</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -99344,17 +99229,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>42358</t>
+          <t>63214</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Nurislom</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>HORNSBY</t>
+          <t>TUKHTASIN UGLI</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -99366,17 +99251,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>42463</t>
+          <t>89760</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Oleksandr</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>MEHAK</t>
+          <t>SIVKOV</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -99388,17 +99273,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>42735</t>
+          <t>127223</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Nelson Roberto</t>
+          <t>Aliaksandr</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>GERINGER SALLETE</t>
+          <t>YERMAKOU</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -99410,132 +99295,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>133041</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Vitalii</t>
+          <t>Hong</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>TSURKAN</t>
+          <t>ZHANG</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>52228</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Aleksey</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>MOCHALOV</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>54666</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Nasreddine</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>BAGHDADI</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>63214</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Nurislom</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>TUKHTASIN UGLI</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>89760</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Oleksandr</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>SIVKOV</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>127223</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Aliaksandr</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>YERMAKOU</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>

--- a/events/Poznan_2012_WC/Poznan_2012_WC_Results.xlsx
+++ b/events/Poznan_2012_WC/Poznan_2012_WC_Results.xlsx
@@ -49583,11 +49583,6 @@
           <t>1:58.321</t>
         </is>
       </c>
-      <c r="S758" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -64101,11 +64096,6 @@
           <t>1:53.821</t>
         </is>
       </c>
-      <c r="S985" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
@@ -83311,11 +83301,6 @@
       <c r="P1281" t="inlineStr">
         <is>
           <t>1:54.544</t>
-        </is>
-      </c>
-      <c r="S1281" t="inlineStr">
-        <is>
-          <t>133041</t>
         </is>
       </c>
     </row>
@@ -92799,7 +92784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D296"/>
+  <dimension ref="A1:D295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99292,28 +99277,6 @@
         </is>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Hong</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>ZHANG</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Poznan_2012_WC/Poznan_2012_WC_Results.xlsx
+++ b/events/Poznan_2012_WC/Poznan_2012_WC_Results.xlsx
@@ -8150,6 +8150,11 @@
           <t>5:04.458</t>
         </is>
       </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12233,6 +12238,11 @@
           <t>36499</t>
         </is>
       </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>36501</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -14658,6 +14668,11 @@
           <t>1:40.350</t>
         </is>
       </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
       <c r="S223" t="inlineStr">
         <is>
           <t>36164</t>
@@ -21531,6 +21546,11 @@
       <c r="L331" t="n">
         <v>9</v>
       </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
       <c r="X331" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -29416,6 +29436,11 @@
           <t>2:24.594</t>
         </is>
       </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -42855,6 +42880,11 @@
           <t>89760</t>
         </is>
       </c>
+      <c r="U659" t="inlineStr">
+        <is>
+          <t>46397</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -47858,6 +47888,11 @@
           <t>1:44.057</t>
         </is>
       </c>
+      <c r="R733" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
       <c r="T733" t="inlineStr">
         <is>
           <t>36164</t>
@@ -53548,6 +53583,11 @@
           <t>0:41.545</t>
         </is>
       </c>
+      <c r="R821" t="inlineStr">
+        <is>
+          <t>36501</t>
+        </is>
+      </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
@@ -55833,6 +55873,11 @@
           <t>0:48.395</t>
         </is>
       </c>
+      <c r="R857" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
@@ -68235,6 +68280,11 @@
       <c r="L1051" t="n">
         <v>7</v>
       </c>
+      <c r="R1051" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
       <c r="X1051" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -88223,6 +88273,11 @@
           <t>23:32.709</t>
         </is>
       </c>
+      <c r="R1355" t="inlineStr">
+        <is>
+          <t>46397</t>
+        </is>
+      </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
@@ -88653,6 +88708,11 @@
       </c>
       <c r="L1362" t="n">
         <v>2</v>
+      </c>
+      <c r="R1362" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
       </c>
       <c r="X1362" t="inlineStr">
         <is>
@@ -92784,7 +92844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D295"/>
+  <dimension ref="A1:D299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99277,6 +99337,94 @@
         </is>
       </c>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Vicente</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>GONZALES</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>36501</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Jesus</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>COLMENARES</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>ANYSHINA</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>46397</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Eduard</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>SHEMUTILO</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Poznan_2012_WC/Poznan_2012_WC_Results.xlsx
+++ b/events/Poznan_2012_WC/Poznan_2012_WC_Results.xlsx
@@ -28621,6 +28621,11 @@
           <t>2:06.392</t>
         </is>
       </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -36305,6 +36310,11 @@
           <t>2:04.907</t>
         </is>
       </c>
+      <c r="R559" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -55243,6 +55253,11 @@
           <t>0:43.210</t>
         </is>
       </c>
+      <c r="R847" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -68415,6 +68430,11 @@
           <t>0:42.977</t>
         </is>
       </c>
+      <c r="R1053" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
@@ -79138,6 +79158,11 @@
           <t>0:42.769</t>
         </is>
       </c>
+      <c r="R1218" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
@@ -86170,6 +86195,11 @@
       <c r="P1324" t="inlineStr">
         <is>
           <t>2:08.876</t>
+        </is>
+      </c>
+      <c r="R1324" t="inlineStr">
+        <is>
+          <t>36633</t>
         </is>
       </c>
     </row>
@@ -92844,7 +92874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D299"/>
+  <dimension ref="A1:D300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99425,6 +99455,28 @@
         </is>
       </c>
     </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>NIVALTER</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>SANTOS</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
